--- a/outputs/daily/hr_rankings_2026-09-26_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-26_full.xlsx
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19228,7 +19228,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -25248,7 +25248,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -39223,47 +39223,47 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>805805</t>
+          <t>699115</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>Carlos Jorge</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T19:07:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>543135</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39272,7 +39272,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39286,62 +39286,58 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>26.9</v>
+        <v>10</v>
       </c>
       <c r="Q142" t="n">
-        <v>42.3</v>
+        <v>33.4</v>
       </c>
       <c r="R142" t="n">
-        <v>27.1</v>
+        <v>43.9</v>
       </c>
       <c r="S142" t="n">
-        <v>47.9</v>
+        <v>93.2</v>
       </c>
       <c r="T142" t="n">
         <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>74.2</v>
+        <v>39.8</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -39361,27 +39357,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 7.7 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39391,104 +39387,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>97.0592</t>
+          <t>93.3196</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.4045</t>
+          <t>0.3414</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>25.04</t>
-        </is>
-      </c>
-      <c r="BG142" t="inlineStr"/>
-      <c r="BH142" t="inlineStr"/>
+          <t>25.74</t>
+        </is>
+      </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH142" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -39499,47 +39503,47 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>699115</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Carlos Jorge</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-26T19:07:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -39548,7 +39552,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -39562,61 +39566,65 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>10</v>
+        <v>23.7</v>
       </c>
       <c r="Q143" t="n">
-        <v>33.4</v>
+        <v>36.4</v>
       </c>
       <c r="R143" t="n">
-        <v>43.9</v>
+        <v>23.2</v>
       </c>
       <c r="S143" t="n">
-        <v>93.2</v>
+        <v>59.8</v>
       </c>
       <c r="T143" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U143" t="n">
-        <v>39.8</v>
+        <v>97</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W143" t="inlineStr">
+      <c r="Z143" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -39633,27 +39641,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 7.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -39663,112 +39671,104 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>93.3196</t>
+          <t>98.5257</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.3795</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1368</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>71.08</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>44.88</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3414</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>25.74</t>
-        </is>
-      </c>
-      <c r="BG143" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH143" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>29.09</t>
+        </is>
+      </c>
+      <c r="BG143" t="inlineStr"/>
+      <c r="BH143" t="inlineStr"/>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -39779,22 +39779,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695336</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -39814,12 +39814,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -39842,26 +39842,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>23.7</v>
+        <v>36.6</v>
       </c>
       <c r="Q144" t="n">
-        <v>36.4</v>
+        <v>45.3</v>
       </c>
       <c r="R144" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S144" t="n">
         <v>59.8</v>
       </c>
       <c r="T144" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U144" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -39917,27 +39917,27 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 1/24, 0 HR</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
@@ -39947,104 +39947,104 @@
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>98.5257</t>
+          <t>100.5499</t>
         </is>
       </c>
       <c r="AR144" t="inlineStr">
         <is>
-          <t>0.3795</t>
+          <t>0.3888</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>0.1368</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.3034</t>
         </is>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD144" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4125</t>
         </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG144" t="inlineStr"/>
       <c r="BH144" t="inlineStr"/>
       <c r="BI144" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ144" t="inlineStr"/>
@@ -40055,22 +40055,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>695336</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Thomas Saggese</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -40090,12 +40090,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -40104,7 +40104,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -40118,26 +40118,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>36.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q145" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="R145" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S145" t="n">
         <v>59.8</v>
       </c>
       <c r="T145" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40193,27 +40193,27 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/24, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40223,104 +40223,104 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>100.5499</t>
+          <t>98.6019</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.3888</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.1423</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.3034</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1313</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4125</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
       <c r="BH145" t="inlineStr"/>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -40331,27 +40331,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-27T01:40:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -40366,12 +40366,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>27.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q146" t="n">
-        <v>42.9</v>
+        <v>33.8</v>
       </c>
       <c r="R146" t="n">
-        <v>23.2</v>
+        <v>30.9</v>
       </c>
       <c r="S146" t="n">
         <v>59.8</v>
@@ -40413,7 +40413,7 @@
         <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>26.2</v>
+        <v>40.3</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -40469,12 +40469,12 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -40484,12 +40484,12 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 4/15, 1 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -40499,104 +40499,104 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>98.6019</t>
+          <t>99.3327</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.3919</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1423</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>70.69</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.1494</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40607,27 +40607,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>805805</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-27T01:40:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -40637,17 +40637,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>543135</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -40656,7 +40656,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -40670,26 +40670,26 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="Q147" t="n">
-        <v>33.8</v>
+        <v>42.3</v>
       </c>
       <c r="R147" t="n">
-        <v>30.9</v>
+        <v>27.1</v>
       </c>
       <c r="S147" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T147" t="n">
         <v>80</v>
       </c>
       <c r="U147" t="n">
-        <v>40.3</v>
+        <v>74.2</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -40728,7 +40728,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -40745,27 +40745,27 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -40775,104 +40775,104 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>99.3327</t>
+          <t>97.0592</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.3919</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.4045</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.1494</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
       <c r="BH147" t="inlineStr"/>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -41184,7 +41184,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -42292,7 +42292,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -49663,22 +49663,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>805346</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ben Ross</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -49693,17 +49693,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Jack Ralston</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>543135</t>
+          <t>667652</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -49712,7 +49712,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -49726,26 +49726,26 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P180" t="n">
-        <v>32.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q180" t="n">
-        <v>42.3</v>
+        <v>49.1</v>
       </c>
       <c r="R180" t="n">
-        <v>27.1</v>
+        <v>21.5</v>
       </c>
       <c r="S180" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T180" t="n">
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>17.3</v>
+        <v>30.2</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
@@ -49784,7 +49784,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr"/>
@@ -49801,12 +49801,12 @@
       </c>
       <c r="AH180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -49816,119 +49816,119 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>93.4311</t>
+          <t>96.2299</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.0987</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.2955</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.1168</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>0.4045</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.204</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
       <c r="BH180" t="inlineStr"/>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr"/>
@@ -49939,27 +49939,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -49969,26 +49969,26 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Jack Ralston</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>667652</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>35.7</v>
+        <v>35.4</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -50002,26 +50002,26 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>9.699999999999999</v>
+        <v>46.7</v>
       </c>
       <c r="Q181" t="n">
-        <v>49.1</v>
+        <v>18.5</v>
       </c>
       <c r="R181" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S181" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T181" t="n">
         <v>50</v>
       </c>
       <c r="U181" t="n">
-        <v>30.2</v>
+        <v>4.2</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
@@ -50077,12 +50077,12 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
@@ -50092,119 +50092,119 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.8% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>49.41</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>96.2299</t>
+          <t>103.8654</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.4138</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>0.0987</t>
+          <t>0.1582</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>0.2955</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>0.1168</t>
+          <t>0.1349</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
       <c r="BH181" t="inlineStr"/>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr"/>
@@ -50215,32 +50215,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -50250,21 +50250,21 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Kirby Yates</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>489446</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
@@ -50278,65 +50278,61 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P182" t="n">
-        <v>46.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q182" t="n">
-        <v>18.5</v>
+        <v>40.1</v>
       </c>
       <c r="R182" t="n">
-        <v>27.6</v>
+        <v>59.6</v>
       </c>
       <c r="S182" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T182" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U182" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr"/>
@@ -50353,12 +50349,12 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -50368,119 +50364,127 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 0/11, 0 HR</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.8% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>85.77</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>103.8654</t>
+          <t>95.725</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>0.4138</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>0.1582</t>
+          <t>0.0893</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.2903</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>77.58</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>40.47</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>0.1349</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3506</t>
         </is>
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>25.8</t>
-        </is>
-      </c>
-      <c r="BG182" t="inlineStr"/>
-      <c r="BH182" t="inlineStr"/>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH182" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr"/>
@@ -50491,12 +50495,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>595879</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Javier Báez</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -50521,7 +50525,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -50540,7 +50544,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -50554,11 +50558,11 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P183" t="n">
-        <v>6.4</v>
+        <v>14.6</v>
       </c>
       <c r="Q183" t="n">
         <v>40.1</v>
@@ -50567,13 +50571,13 @@
         <v>59.6</v>
       </c>
       <c r="S183" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T183" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U183" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
@@ -50587,7 +50591,7 @@
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
@@ -50625,27 +50629,27 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/11, 0 HR</t>
+          <t>Last 7 games: 2/18, 1 HR</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
@@ -50655,67 +50659,67 @@
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>85.77</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>95.725</t>
+          <t>97.8075</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>0.0893</t>
+          <t>0.0961</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>0.2903</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>73.36</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>40.47</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
@@ -50771,54 +50775,42 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>595879</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Javier Báez</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-09-26T17:10:00Z</t>
+          <t>2026-09-26T23:15:00Z</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Kirby Yates</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>489446</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
         <v>35.1</v>
       </c>
@@ -50834,61 +50826,65 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P184" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="Q184" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R184" t="n">
-        <v>59.6</v>
+        <v>34.3</v>
       </c>
       <c r="S184" t="n">
-        <v>44.8</v>
+        <v>59.8</v>
       </c>
       <c r="T184" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U184" t="n">
-        <v>18.3</v>
+        <v>22</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W184" t="inlineStr">
+      <c r="Z184" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr"/>
@@ -50905,27 +50901,27 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 1 HR</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
@@ -50935,112 +50931,80 @@
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>97.8075</t>
+          <t>97.1046</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>0.0961</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>73.36</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>0.1266</t>
-        </is>
-      </c>
-      <c r="BA184" t="inlineStr">
-        <is>
-          <t>7.96</t>
-        </is>
-      </c>
-      <c r="BB184" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="BC184" t="inlineStr">
-        <is>
-          <t>90.53</t>
-        </is>
-      </c>
-      <c r="BD184" t="inlineStr">
-        <is>
-          <t>0.3506</t>
-        </is>
-      </c>
-      <c r="BE184" t="inlineStr">
-        <is>
-          <t>0.1351</t>
-        </is>
-      </c>
-      <c r="BF184" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="BG184" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH184" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>0.1337</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr"/>
+      <c r="BB184" t="inlineStr"/>
+      <c r="BC184" t="inlineStr"/>
+      <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr"/>
@@ -51051,27 +51015,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>518595</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Travis d'Arnaud</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-09-26T23:15:00Z</t>
+          <t>2026-09-27T01:40:00Z</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -51081,12 +51045,24 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Kade Anderson</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>807739</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L185" t="n">
         <v>35.1</v>
       </c>
@@ -51102,26 +51078,26 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P185" t="n">
-        <v>15.7</v>
+        <v>27.7</v>
       </c>
       <c r="Q185" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R185" t="n">
-        <v>34.3</v>
+        <v>25.4</v>
       </c>
       <c r="S185" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T185" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U185" t="n">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="V185" t="inlineStr">
         <is>
@@ -51135,7 +51111,7 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -51160,7 +51136,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr"/>
@@ -51177,12 +51153,12 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
@@ -51192,12 +51168,12 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
@@ -51207,80 +51183,104 @@
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>97.1046</t>
+          <t>97.5183</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3047</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2445</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>0.1337</t>
-        </is>
-      </c>
-      <c r="BA185" t="inlineStr"/>
-      <c r="BB185" t="inlineStr"/>
-      <c r="BC185" t="inlineStr"/>
-      <c r="BD185" t="inlineStr"/>
-      <c r="BE185" t="inlineStr"/>
-      <c r="BF185" t="inlineStr"/>
+          <t>0.0991</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>88.1</t>
+        </is>
+      </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>0.405</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
       <c r="BG185" t="inlineStr"/>
       <c r="BH185" t="inlineStr"/>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr"/>
@@ -51291,56 +51291,56 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>518595</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Travis d'Arnaud</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-09-27T01:40:00Z</t>
+          <t>2026-09-26T16:35:00Z</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Jonah Tong</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>804636</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -51354,65 +51354,61 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>27.7</v>
+        <v>16</v>
       </c>
       <c r="Q186" t="n">
-        <v>38.7</v>
+        <v>35.8</v>
       </c>
       <c r="R186" t="n">
-        <v>25.4</v>
+        <v>44.7</v>
       </c>
       <c r="S186" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T186" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U186" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -51434,7 +51430,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
@@ -51444,119 +51440,127 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 4.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.0% barrel, 2.3 HR allowed</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>97.5183</t>
+          <t>97.4349</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>0.3047</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>0.2445</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>26.21</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>0.0991</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="BD186" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="BE186" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="BG186" t="inlineStr"/>
-      <c r="BH186" t="inlineStr"/>
+          <t>33.24</t>
+        </is>
+      </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr"/>
@@ -51567,47 +51571,47 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-09-26T16:35:00Z</t>
+          <t>2026-09-26T23:15:00Z</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Jonah Tong</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>804636</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -51630,61 +51634,65 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q187" t="n">
-        <v>35.8</v>
+        <v>41.5</v>
       </c>
       <c r="R187" t="n">
-        <v>44.7</v>
+        <v>34.3</v>
       </c>
       <c r="S187" t="n">
-        <v>52.4</v>
+        <v>59.8</v>
       </c>
       <c r="T187" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U187" t="n">
-        <v>7</v>
+        <v>13.6</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr">
+      <c r="Z187" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -51701,12 +51709,12 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -51716,127 +51724,119 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.0% barrel, 2.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>97.4349</t>
+          <t>98.1205</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>0.2877</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>26.21</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD187" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.3951</t>
         </is>
       </c>
       <c r="BE187" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="BG187" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH187" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+          <t>23.09</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr"/>
@@ -51847,27 +51847,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-09-26T23:15:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -51877,17 +51877,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -51896,7 +51896,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -51914,22 +51914,22 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>11</v>
+        <v>7.3</v>
       </c>
       <c r="Q188" t="n">
-        <v>41.5</v>
+        <v>45.3</v>
       </c>
       <c r="R188" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S188" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T188" t="n">
         <v>80</v>
       </c>
       <c r="U188" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
@@ -51985,12 +51985,12 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
@@ -52000,12 +52000,12 @@
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 0/18, 0 HR</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
@@ -52015,104 +52015,104 @@
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>98.1205</t>
+          <t>95.7371</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>0.3951</t>
+          <t>0.4125</t>
         </is>
       </c>
       <c r="BE188" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
       <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr"/>
@@ -52123,27 +52123,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>663494</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-27T00:40:00Z</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -52153,24 +52153,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="n">
         <v>34.7</v>
       </c>
@@ -52186,26 +52174,26 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>7.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q189" t="n">
-        <v>45.3</v>
+        <v>41.2</v>
       </c>
       <c r="R189" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S189" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T189" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U189" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
@@ -52219,7 +52207,7 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -52244,7 +52232,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr"/>
@@ -52261,27 +52249,27 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/18, 0 HR</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
@@ -52291,104 +52279,80 @@
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>35.53</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>95.7371</t>
+          <t>98.3374</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.2913</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>0.103</t>
-        </is>
-      </c>
-      <c r="BA189" t="inlineStr">
-        <is>
-          <t>8.08</t>
-        </is>
-      </c>
-      <c r="BB189" t="inlineStr">
-        <is>
-          <t>44.43</t>
-        </is>
-      </c>
-      <c r="BC189" t="inlineStr">
-        <is>
-          <t>90.11</t>
-        </is>
-      </c>
-      <c r="BD189" t="inlineStr">
-        <is>
-          <t>0.4125</t>
-        </is>
-      </c>
-      <c r="BE189" t="inlineStr">
-        <is>
-          <t>0.1574</t>
-        </is>
-      </c>
-      <c r="BF189" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
+          <t>0.1183</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
       <c r="BG189" t="inlineStr"/>
       <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr"/>
@@ -52399,27 +52363,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-09-27T00:40:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -52429,14 +52393,26 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Brent Suter</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>608718</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L190" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -52450,26 +52426,26 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>19.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q190" t="n">
-        <v>41.2</v>
+        <v>26.8</v>
       </c>
       <c r="R190" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="S190" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T190" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U190" t="n">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -52483,7 +52459,7 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
@@ -52508,7 +52484,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr"/>
@@ -52525,7 +52501,7 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
@@ -52540,12 +52516,12 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
@@ -52555,80 +52531,104 @@
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>98.3374</t>
+          <t>97.4924</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3518</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.0858</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.2913</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.32</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1183</t>
-        </is>
-      </c>
-      <c r="BA190" t="inlineStr"/>
-      <c r="BB190" t="inlineStr"/>
-      <c r="BC190" t="inlineStr"/>
-      <c r="BD190" t="inlineStr"/>
-      <c r="BE190" t="inlineStr"/>
-      <c r="BF190" t="inlineStr"/>
+          <t>0.1572</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>31.36</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>86.29</t>
+        </is>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>0.4033</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>0.1519</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>23.51</t>
+        </is>
+      </c>
       <c r="BG190" t="inlineStr"/>
       <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -52639,27 +52639,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -52669,22 +52669,22 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Brent Suter</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>608718</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -52702,26 +52702,26 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q191" t="n">
-        <v>26.8</v>
+        <v>38</v>
       </c>
       <c r="R191" t="n">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
       <c r="S191" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T191" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U191" t="n">
-        <v>53.9</v>
+        <v>28.2</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -52777,27 +52777,27 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -52807,104 +52807,104 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.52</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>97.4924</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.3518</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.0858</t>
+          <t>0.0734</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>19.32</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.0747</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE191" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
       <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -52915,22 +52915,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -52945,17 +52945,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -52964,7 +52964,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -52978,26 +52978,26 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.8</v>
+        <v>14.2</v>
       </c>
       <c r="Q192" t="n">
-        <v>38</v>
+        <v>45.3</v>
       </c>
       <c r="R192" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S192" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T192" t="n">
         <v>80</v>
       </c>
       <c r="U192" t="n">
-        <v>28.2</v>
+        <v>16.1</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -53053,12 +53053,12 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -53068,12 +53068,12 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -53083,104 +53083,104 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>84.52</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>97.4595</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>0.0734</t>
+          <t>0.1046</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2736</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>0.0747</t>
+          <t>0.1046</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4125</t>
         </is>
       </c>
       <c r="BE192" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
       <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ192" t="inlineStr"/>
@@ -53191,27 +53191,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>640459</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -53221,26 +53221,26 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Brent Suter</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>608718</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>34.4</v>
+        <v>34.1</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -53254,26 +53254,26 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P193" t="n">
-        <v>14.2</v>
+        <v>30.9</v>
       </c>
       <c r="Q193" t="n">
-        <v>45.3</v>
+        <v>26.8</v>
       </c>
       <c r="R193" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S193" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T193" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U193" t="n">
-        <v>16.1</v>
+        <v>32</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -53329,12 +53329,12 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -53344,12 +53344,12 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Contact streak: 2/6 over last 7 games</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -53359,104 +53359,104 @@
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>36.46</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>97.4595</t>
+          <t>98.6055</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.2797</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>0.1046</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>0.2736</t>
+          <t>0.2227</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.86</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>54.52</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>0.1046</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>0.4125</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="BE193" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr"/>
       <c r="BH193" t="inlineStr"/>
       <c r="BI193" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ193" t="inlineStr"/>
@@ -53467,27 +53467,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>640459</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-27T00:40:00Z</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -53497,26 +53497,14 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Brent Suter</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>608718</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -53530,26 +53518,26 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>30.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q194" t="n">
-        <v>26.8</v>
+        <v>41.2</v>
       </c>
       <c r="R194" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="S194" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T194" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U194" t="n">
-        <v>32</v>
+        <v>10.8</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
@@ -53563,7 +53551,7 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
@@ -53588,7 +53576,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr"/>
@@ -53605,12 +53593,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -53620,12 +53608,12 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Contact streak: 2/6 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -53635,104 +53623,80 @@
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>36.46</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>98.6055</t>
+          <t>94.9526</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>0.2797</t>
+          <t>0.3303</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.0848</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>0.2227</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>66.89</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>0.1911</t>
-        </is>
-      </c>
-      <c r="BA194" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="BB194" t="inlineStr">
-        <is>
-          <t>31.36</t>
-        </is>
-      </c>
-      <c r="BC194" t="inlineStr">
-        <is>
-          <t>86.29</t>
-        </is>
-      </c>
-      <c r="BD194" t="inlineStr">
-        <is>
-          <t>0.4033</t>
-        </is>
-      </c>
-      <c r="BE194" t="inlineStr">
-        <is>
-          <t>0.1519</t>
-        </is>
-      </c>
-      <c r="BF194" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
-      </c>
+          <t>0.1017</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
       <c r="BG194" t="inlineStr"/>
       <c r="BH194" t="inlineStr"/>
       <c r="BI194" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ194" t="inlineStr"/>
@@ -53743,12 +53707,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -53773,14 +53737,14 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -53794,11 +53758,11 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P195" t="n">
-        <v>3.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q195" t="n">
         <v>41.2</v>
@@ -53807,13 +53771,13 @@
         <v>22.6</v>
       </c>
       <c r="S195" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T195" t="n">
         <v>60</v>
       </c>
       <c r="U195" t="n">
-        <v>10.8</v>
+        <v>62.4</v>
       </c>
       <c r="V195" t="inlineStr">
         <is>
@@ -53827,7 +53791,7 @@
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
@@ -53869,22 +53833,22 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL195" t="inlineStr">
@@ -53899,67 +53863,67 @@
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>94.9526</t>
+          <t>97.6767</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>0.3303</t>
+          <t>0.3173</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>0.0848</t>
+          <t>0.1014</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>0.2877</t>
+          <t>0.2847</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>66.89</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>0.1017</t>
+          <t>0.1051</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr"/>
@@ -53983,27 +53947,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-09-27T00:40:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -54016,11 +53980,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Jack Ralston</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>667652</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L196" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -54034,26 +54010,26 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P196" t="n">
         <v>15.4</v>
       </c>
       <c r="Q196" t="n">
-        <v>41.2</v>
+        <v>48.7</v>
       </c>
       <c r="R196" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="S196" t="n">
         <v>47.9</v>
       </c>
       <c r="T196" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U196" t="n">
-        <v>62.4</v>
+        <v>0</v>
       </c>
       <c r="V196" t="inlineStr">
         <is>
@@ -54092,7 +54068,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr"/>
@@ -54109,110 +54085,134 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/26, 0 HR</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>97.6767</t>
+          <t>96.6742</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>0.3173</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>0.1014</t>
+          <t>0.1191</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>0.2847</t>
+          <t>0.2822</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>0.1051</t>
-        </is>
-      </c>
-      <c r="BA196" t="inlineStr"/>
-      <c r="BB196" t="inlineStr"/>
-      <c r="BC196" t="inlineStr"/>
-      <c r="BD196" t="inlineStr"/>
-      <c r="BE196" t="inlineStr"/>
-      <c r="BF196" t="inlineStr"/>
+          <t>0.1467</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>0.411</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>0.204</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
       <c r="BG196" t="inlineStr"/>
       <c r="BH196" t="inlineStr"/>
       <c r="BI196" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ196" t="inlineStr"/>
@@ -54223,27 +54223,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-27T01:40:00Z</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -54258,12 +54258,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Jack Ralston</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>667652</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -54290,13 +54290,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>15.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q197" t="n">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="R197" t="n">
-        <v>21.5</v>
+        <v>30.9</v>
       </c>
       <c r="S197" t="n">
         <v>47.9</v>
@@ -54305,7 +54305,7 @@
         <v>75</v>
       </c>
       <c r="U197" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V197" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr"/>
@@ -54361,12 +54361,12 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -54376,119 +54376,119 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>96.6742</t>
+          <t>97.7142</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.1326</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>0.2822</t>
+          <t>0.2823</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="BE197" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.1494</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
       <c r="BH197" t="inlineStr"/>
       <c r="BI197" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ197" t="inlineStr"/>
@@ -54499,27 +54499,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-09-27T01:40:00Z</t>
+          <t>2026-09-26T20:05:00Z</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -54529,26 +54529,26 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>33.5</v>
+        <v>32.6</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -54566,22 +54566,22 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>21.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q198" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
       <c r="R198" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S198" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T198" t="n">
         <v>75</v>
       </c>
       <c r="U198" t="n">
-        <v>9.300000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="V198" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
@@ -54620,7 +54620,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr"/>
@@ -54637,134 +54637,134 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>97.7142</t>
+          <t>98.7097</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>0.1326</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>0.2823</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.382</t>
         </is>
       </c>
       <c r="BE198" t="inlineStr">
         <is>
-          <t>0.1494</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr"/>
       <c r="BH198" t="inlineStr"/>
       <c r="BI198" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ198" t="inlineStr"/>
@@ -54775,27 +54775,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>805300</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-26T20:05:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -54805,17 +54805,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Brent Suter</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>608718</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -54838,26 +54838,26 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="Q199" t="n">
-        <v>36.2</v>
+        <v>26.8</v>
       </c>
       <c r="R199" t="n">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
       <c r="S199" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T199" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U199" t="n">
-        <v>37.4</v>
+        <v>32</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -54896,7 +54896,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr"/>
@@ -54913,7 +54913,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
@@ -54923,124 +54923,124 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>36.57</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>98.7097</t>
+          <t>98.5574</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.1153</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3239</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>70.29</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>40.88</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -55051,56 +55051,56 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>805300</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T19:07:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Brent Suter</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>608718</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -55114,65 +55114,61 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P200" t="n">
-        <v>20.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q200" t="n">
-        <v>26.8</v>
+        <v>54</v>
       </c>
       <c r="R200" t="n">
-        <v>21.5</v>
+        <v>43.9</v>
       </c>
       <c r="S200" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T200" t="n">
         <v>50</v>
       </c>
       <c r="U200" t="n">
-        <v>32</v>
+        <v>0.8</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -55189,7 +55185,7 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
@@ -55204,12 +55200,12 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -55219,104 +55215,112 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>84.92</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>98.5574</t>
+          <t>94.5834</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.3239</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>70.29</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>40.88</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.467</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>23.51</t>
-        </is>
-      </c>
-      <c r="BG200" t="inlineStr"/>
-      <c r="BH200" t="inlineStr"/>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG200" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH200" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -55327,47 +55331,47 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>691182</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-09-26T19:07:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -55376,7 +55380,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -55390,61 +55394,65 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q201" t="n">
-        <v>54</v>
+        <v>43.4</v>
       </c>
       <c r="R201" t="n">
-        <v>43.9</v>
+        <v>27.6</v>
       </c>
       <c r="S201" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T201" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U201" t="n">
-        <v>0.8</v>
+        <v>17.3</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W201" t="inlineStr">
+      <c r="Z201" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -55461,12 +55469,12 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
@@ -55476,12 +55484,12 @@
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 18.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.5% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -55491,112 +55499,104 @@
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>84.92</t>
+          <t>83.96</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>94.5834</t>
+          <t>96.0789</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.2697</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1832</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.4279</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="BG201" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH201" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>
@@ -55607,27 +55607,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>691182</t>
+          <t>691858</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Jared Serna</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -55637,26 +55637,26 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Brent Suter</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>608718</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>31.9</v>
+        <v>31.4</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -55674,22 +55674,22 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q202" t="n">
-        <v>43.4</v>
+        <v>26.8</v>
       </c>
       <c r="R202" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S202" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T202" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U202" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr"/>
@@ -55745,12 +55745,12 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -55760,12 +55760,12 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 1/11, 0 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.5% barrel, 15.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
@@ -55775,104 +55775,104 @@
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>83.96</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>96.0789</t>
+          <t>98.077</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>0.1013</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>0.2697</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>0.1832</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="BD202" t="inlineStr">
         <is>
-          <t>0.4279</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="BE202" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr"/>
       <c r="BH202" t="inlineStr"/>
       <c r="BI202" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ202" t="inlineStr"/>
@@ -55883,27 +55883,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>691858</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jared Serna</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -55913,22 +55913,22 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Brent Suter</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>608718</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L203" t="n">
@@ -55950,22 +55950,22 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q203" t="n">
-        <v>26.8</v>
+        <v>42.9</v>
       </c>
       <c r="R203" t="n">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
       <c r="S203" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T203" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U203" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V203" t="inlineStr">
         <is>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y203" t="inlineStr">
@@ -56004,7 +56004,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr"/>
@@ -56021,12 +56021,12 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
@@ -56036,12 +56036,12 @@
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/11, 0 HR</t>
+          <t>Last 7 games: 4/16, 0 HR</t>
         </is>
       </c>
       <c r="AL203" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
         </is>
       </c>
       <c r="AM203" t="inlineStr">
@@ -56051,104 +56051,104 @@
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>98.077</t>
+          <t>98.7573</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.0749</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.2531</t>
         </is>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0994</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="BD203" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE203" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="BG203" t="inlineStr"/>
       <c r="BH203" t="inlineStr"/>
       <c r="BI203" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ203" t="inlineStr"/>
@@ -56159,27 +56159,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -56189,17 +56189,17 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>543135</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -56208,7 +56208,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -56222,26 +56222,26 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P204" t="n">
-        <v>11.5</v>
+        <v>17.4</v>
       </c>
       <c r="Q204" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="R204" t="n">
-        <v>23.2</v>
+        <v>27.1</v>
       </c>
       <c r="S204" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T204" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U204" t="n">
-        <v>19.5</v>
+        <v>3.4</v>
       </c>
       <c r="V204" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y204" t="inlineStr">
@@ -56280,7 +56280,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr"/>
@@ -56297,12 +56297,12 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
@@ -56312,12 +56312,12 @@
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL204" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
@@ -56327,67 +56327,67 @@
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>98.7573</t>
+          <t>97.517</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>0.0749</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>0.2531</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>0.0994</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
@@ -56397,34 +56397,34 @@
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="BD204" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.4045</t>
         </is>
       </c>
       <c r="BE204" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="BG204" t="inlineStr"/>
       <c r="BH204" t="inlineStr"/>
       <c r="BI204" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ204" t="inlineStr"/>
@@ -57768,7 +57768,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -64146,7 +64146,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -64426,7 +64426,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
